--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -81,7 +81,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060348</t>
+          <t xml:space="preserve">100248845, 100248847</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -90,7 +90,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>5039</v>
+        <v>1512</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128107</t>
+          <t xml:space="preserve">2128199</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>2025</v>
+        <v>4250</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128199</t>
+          <t xml:space="preserve">2146774</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -340,7 +340,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>4250</v>
+        <v>1219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142154</t>
+          <t xml:space="preserve">2146774</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F8">
-        <v>2362</v>
+        <v>2580</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142154</t>
+          <t xml:space="preserve">2148852</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>822</v>
+        <v>906</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142154</t>
+          <t xml:space="preserve">2161091</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>810</v>
+        <v>5732</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146774</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F11">
-        <v>1219</v>
+        <v>368</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146774</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F12">
-        <v>2580</v>
+        <v>1215</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F13">
-        <v>408</v>
+        <v>737</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F14">
-        <v>375</v>
+        <v>734</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148852</t>
+          <t xml:space="preserve">2161248</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>906</v>
+        <v>1262</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161091</t>
+          <t xml:space="preserve">2165282</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F16">
-        <v>5732</v>
+        <v>735</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2165621</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2165621</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F18">
-        <v>1215</v>
+        <v>514</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F19">
-        <v>737</v>
+        <v>352</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F20">
-        <v>734</v>
+        <v>352</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161248</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F21">
-        <v>1262</v>
+        <v>1587</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165282</t>
+          <t xml:space="preserve">2201021</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>735</v>
+        <v>1428</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165621</t>
+          <t xml:space="preserve">7010716</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>324</v>
+        <v>2278</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165621</t>
+          <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>514</v>
+        <v>1340</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F25">
-        <v>352</v>
+        <v>1463</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">714721, 2162134</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>352</v>
+        <v>1904</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">7495520</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>1587</v>
+        <v>285</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201021</t>
+          <t xml:space="preserve">8011213</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28">
-        <v>1428</v>
+        <v>267</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010716</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F29">
-        <v>2278</v>
+        <v>432</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,30 +1481,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2161923</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>1414</v>
+        <v>312</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019744</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1531,30 +1531,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2128322</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>1539</v>
+        <v>724</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019918</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1581,30 +1581,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2142154</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>1500</v>
+        <v>2362</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019887</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2142154</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>747</v>
+        <v>822</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019887</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1681,30 +1681,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2142154</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>1534</v>
+        <v>810</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019887</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1731,30 +1731,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2128322</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>1504</v>
+        <v>557</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020052</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">714196, 8856710</t>
+          <t xml:space="preserve">2128136</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="F36">
-        <v>1340</v>
+        <v>584</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311120438</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">714196, 8856710</t>
+          <t xml:space="preserve">8856618</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>1463</v>
+        <v>357</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311120462</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1881,30 +1881,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">714721, 2162134</t>
+          <t xml:space="preserve">8856618</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>1904</v>
+        <v>357</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311120462</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1931,30 +1931,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7495520</t>
+          <t xml:space="preserve">8856618</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311120447</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -1981,30 +1981,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011213</t>
+          <t xml:space="preserve">8856618</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F40">
-        <v>267</v>
+        <v>443</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311120447</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2031,30 +2031,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">2147632</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>432</v>
+        <v>324</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311127421</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161923</t>
+          <t xml:space="preserve">2147632</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019744</t>
+          <t xml:space="preserve">311127428</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-31</t>
+          <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128322</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43">
-        <v>724</v>
+        <v>1818</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019918</t>
+          <t xml:space="preserve">311129908</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-03</t>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128322</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F44">
-        <v>557</v>
+        <v>5611</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020052</t>
+          <t xml:space="preserve">311129908</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-07</t>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128136</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F45">
-        <v>584</v>
+        <v>2415</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120438</t>
+          <t xml:space="preserve">311129908</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856618</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F46">
-        <v>357</v>
+        <v>1064</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120462</t>
+          <t xml:space="preserve">311129908</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856618</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>357</v>
+        <v>1726</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120462</t>
+          <t xml:space="preserve">311130107</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856618</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F48">
-        <v>377</v>
+        <v>525</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120447</t>
+          <t xml:space="preserve">311131087</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856618</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F49">
-        <v>443</v>
+        <v>525</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120447</t>
+          <t xml:space="preserve">311131087</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856711</t>
+          <t xml:space="preserve">2201019</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F50">
-        <v>1452</v>
+        <v>2111</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123167</t>
+          <t xml:space="preserve">311131092</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-03</t>
+          <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147632</t>
+          <t xml:space="preserve">2142493</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="F51">
-        <v>324</v>
+        <v>667</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127421</t>
+          <t xml:space="preserve">311131989</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-03</t>
+          <t xml:space="preserve">2025-08-31</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147632</t>
+          <t xml:space="preserve">2142054</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127428</t>
+          <t xml:space="preserve">311132386</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-03</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201019</t>
+          <t xml:space="preserve">2146021</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>2111</v>
+        <v>324</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129203</t>
+          <t xml:space="preserve">311133694</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-14</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2146021</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>1818</v>
+        <v>374</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129908</t>
+          <t xml:space="preserve">311133694</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-19</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2169189</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>5611</v>
+        <v>526</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129908</t>
+          <t xml:space="preserve">311133717</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-19</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">9208734</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>2415</v>
+        <v>311</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129908</t>
+          <t xml:space="preserve">311133714</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-19</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2161612</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1064</v>
+        <v>359</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129908</t>
+          <t xml:space="preserve">311134097</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-19</t>
+          <t xml:space="preserve">2025-09-11</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">8078292</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,16 +2890,16 @@
         </is>
       </c>
       <c r="F58">
-        <v>1726</v>
+        <v>375</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311130107</t>
+          <t xml:space="preserve">311134621</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-20</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2167951</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>525</v>
+        <v>568</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131087</t>
+          <t xml:space="preserve">311136636</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-26</t>
+          <t xml:space="preserve">2025-09-25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2148252</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>525</v>
+        <v>485</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131087</t>
+          <t xml:space="preserve">311138942</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-26</t>
+          <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142493</t>
+          <t xml:space="preserve">2148252</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>667</v>
+        <v>438</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131989</t>
+          <t xml:space="preserve">311138942</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-31</t>
+          <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142054</t>
+          <t xml:space="preserve">7141252</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="F62">
-        <v>357</v>
+        <v>780</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132386</t>
+          <t xml:space="preserve">311138938</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146021</t>
+          <t xml:space="preserve">2169509</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>324</v>
+        <v>405</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133694</t>
+          <t xml:space="preserve">311141984</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146021</t>
+          <t xml:space="preserve">2201300</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>374</v>
+        <v>469</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133694</t>
+          <t xml:space="preserve">311142030</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169189</t>
+          <t xml:space="preserve">2161799</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>526</v>
+        <v>353</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133717</t>
+          <t xml:space="preserve">311143240</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-11-03</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208734</t>
+          <t xml:space="preserve">2127869</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133714</t>
+          <t xml:space="preserve">311143917</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161612</t>
+          <t xml:space="preserve">2148250</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134097</t>
+          <t xml:space="preserve">311143942</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-11</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8078292</t>
+          <t xml:space="preserve">2148250</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>375</v>
+        <v>452</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134621</t>
+          <t xml:space="preserve">311143941</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-15</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167951</t>
+          <t xml:space="preserve">2161126</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>568</v>
+        <v>473</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136636</t>
+          <t xml:space="preserve">311143930</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-25</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148252</t>
+          <t xml:space="preserve">2161126</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70">
-        <v>485</v>
+        <v>370</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138942</t>
+          <t xml:space="preserve">311143927</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-08</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148252</t>
+          <t xml:space="preserve">2165627</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>438</v>
+        <v>365</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138942</t>
+          <t xml:space="preserve">311143945</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-08</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7141252</t>
+          <t xml:space="preserve">2146881</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>780</v>
+        <v>474</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138938</t>
+          <t xml:space="preserve">311144172</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-08</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856711</t>
+          <t xml:space="preserve">2146986</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138944</t>
+          <t xml:space="preserve">311144177</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-08</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161012</t>
+          <t xml:space="preserve">2165636</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>350</v>
+        <v>485</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141601</t>
+          <t xml:space="preserve">311144235</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-23</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161012</t>
+          <t xml:space="preserve">2201724</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141821</t>
+          <t xml:space="preserve">311144396</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-26</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169509</t>
+          <t xml:space="preserve">7141233</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>405</v>
+        <v>640</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141984</t>
+          <t xml:space="preserve">311144459</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201300</t>
+          <t xml:space="preserve">2161123</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>469</v>
+        <v>547</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142030</t>
+          <t xml:space="preserve">311144697</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161799</t>
+          <t xml:space="preserve">2165634</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143240</t>
+          <t xml:space="preserve">311144674</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-03</t>
+          <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127869</t>
+          <t xml:space="preserve">2201285</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>357</v>
+        <v>547</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143917</t>
+          <t xml:space="preserve">311144642</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148250</t>
+          <t xml:space="preserve">2128200</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>359</v>
+        <v>623</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143942</t>
+          <t xml:space="preserve">311145386</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148250</t>
+          <t xml:space="preserve">2147087</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>452</v>
+        <v>315</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143941</t>
+          <t xml:space="preserve">311145474</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161126</t>
+          <t xml:space="preserve">2161885</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143930</t>
+          <t xml:space="preserve">311145515</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161126</t>
+          <t xml:space="preserve">2161885</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F83">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143927</t>
+          <t xml:space="preserve">311145515</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165627</t>
+          <t xml:space="preserve">2166063</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143945</t>
+          <t xml:space="preserve">311145425</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146881</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F85">
-        <v>474</v>
+        <v>414</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144172</t>
+          <t xml:space="preserve">311145440</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146986</t>
+          <t xml:space="preserve">2201022</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F86">
-        <v>357</v>
+        <v>295</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144177</t>
+          <t xml:space="preserve">311145528</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165636</t>
+          <t xml:space="preserve">2146620</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>485</v>
+        <v>1796</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144235</t>
+          <t xml:space="preserve">311145662</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201724</t>
+          <t xml:space="preserve">2148830</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>480</v>
+        <v>3043</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144396</t>
+          <t xml:space="preserve">311145619</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7141233</t>
+          <t xml:space="preserve">2148830</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>640</v>
+        <v>348</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144459</t>
+          <t xml:space="preserve">311145623</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161123</t>
+          <t xml:space="preserve">2161127</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>547</v>
+        <v>495</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144697</t>
+          <t xml:space="preserve">311145609</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-11</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165634</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>357</v>
+        <v>698</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144674</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-11</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201285</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F92">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144642</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-11</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128107</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F93">
-        <v>792</v>
+        <v>670</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145432</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128200</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F94">
-        <v>623</v>
+        <v>300</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145386</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147087</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F95">
-        <v>315</v>
+        <v>1467</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145474</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161885</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F96">
-        <v>407</v>
+        <v>678</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145515</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161885</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F97">
-        <v>421</v>
+        <v>3285</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145515</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166063</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F98">
-        <v>310</v>
+        <v>1250</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145425</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">7613750</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145440</t>
+          <t xml:space="preserve">311148755</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201022</t>
+          <t xml:space="preserve">2165627</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>295</v>
+        <v>390</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145528</t>
+          <t xml:space="preserve">311149250</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146620</t>
+          <t xml:space="preserve">2165620</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,16 +5040,16 @@
         </is>
       </c>
       <c r="F101">
-        <v>1796</v>
+        <v>410</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145662</t>
+          <t xml:space="preserve">311150128</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-14</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148830</t>
+          <t xml:space="preserve">2142499</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F102">
-        <v>3043</v>
+        <v>1441</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145619</t>
+          <t xml:space="preserve">311151831</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148830</t>
+          <t xml:space="preserve">2142499</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F103">
-        <v>348</v>
+        <v>408</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145623</t>
+          <t xml:space="preserve">311151831</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161127</t>
+          <t xml:space="preserve">100015198</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>495</v>
+        <v>1632</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145609</t>
+          <t xml:space="preserve">311152759</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">8281272</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>698</v>
+        <v>456</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311152766</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F106">
-        <v>521</v>
+        <v>794</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="F107">
-        <v>670</v>
+        <v>817</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>300</v>
+        <v>809</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154281</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F109">
-        <v>1467</v>
+        <v>818</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F110">
-        <v>678</v>
+        <v>794</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">2146071</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>3285</v>
+        <v>1254</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311154518</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-19</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">2148249</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>1250</v>
+        <v>381</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311155372</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">2148249</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F113">
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148357</t>
+          <t xml:space="preserve">311155372</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">2127952</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>1543</v>
+        <v>549</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148357</t>
+          <t xml:space="preserve">311155980</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7613750</t>
+          <t xml:space="preserve">2147293</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>351</v>
+        <v>2473</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148755</t>
+          <t xml:space="preserve">311155979</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165627</t>
+          <t xml:space="preserve">2127703</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>390</v>
+        <v>679</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149250</t>
+          <t xml:space="preserve">311160370</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165620</t>
+          <t xml:space="preserve">2127703</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F117">
-        <v>410</v>
+        <v>520</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150128</t>
+          <t xml:space="preserve">311160369</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-14</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142499</t>
+          <t xml:space="preserve">2127703</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>1441</v>
+        <v>1260</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311151831</t>
+          <t xml:space="preserve">311160371</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142499</t>
+          <t xml:space="preserve">2127703</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F119">
-        <v>408</v>
+        <v>804</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311151831</t>
+          <t xml:space="preserve">311160367</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100015198</t>
+          <t xml:space="preserve">2161719</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>1632</v>
+        <v>301</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152759</t>
+          <t xml:space="preserve">311160365</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-07</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8281272</t>
+          <t xml:space="preserve">2147892</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152766</t>
+          <t xml:space="preserve">311163055</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-07</t>
+          <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">2147892</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F122">
-        <v>794</v>
+        <v>361</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311163055</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">9736444</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>817</v>
+        <v>319</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311166156</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">2167027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>809</v>
+        <v>303</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154281</t>
+          <t xml:space="preserve">311168660</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">2167027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F125">
-        <v>818</v>
+        <v>515</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311168660</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">2167027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F126">
-        <v>794</v>
+        <v>295</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311168660</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146071</t>
+          <t xml:space="preserve">2148652</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>1254</v>
+        <v>6914</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154518</t>
+          <t xml:space="preserve">311172081</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-19</t>
+          <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148249</t>
+          <t xml:space="preserve">2148652</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>381</v>
+        <v>2479</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155372</t>
+          <t xml:space="preserve">311172081</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-25</t>
+          <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148249</t>
+          <t xml:space="preserve">2148652</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F129">
-        <v>381</v>
+        <v>888</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155372</t>
+          <t xml:space="preserve">311172081</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-25</t>
+          <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127952</t>
+          <t xml:space="preserve">2148652</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F130">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155980</t>
+          <t xml:space="preserve">311171998</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147293</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>2473</v>
+        <v>1420</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155979</t>
+          <t xml:space="preserve">311177248</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127703</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>679</v>
+        <v>525</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160370</t>
+          <t xml:space="preserve">311177246</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127703</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F133">
-        <v>520</v>
+        <v>748</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160369</t>
+          <t xml:space="preserve">311177248</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127703</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F134">
-        <v>1260</v>
+        <v>1834</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160371</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127703</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F135">
-        <v>804</v>
+        <v>3570</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160367</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161719</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F136">
-        <v>301</v>
+        <v>4129</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160365</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147892</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F137">
-        <v>441</v>
+        <v>1645</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163055</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-08</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147892</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F138">
-        <v>361</v>
+        <v>5505</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163055</t>
+          <t xml:space="preserve">311181218</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-08</t>
+          <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9736444</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F139">
-        <v>319</v>
+        <v>8516</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166156</t>
+          <t xml:space="preserve">311181218</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167027</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>303</v>
+        <v>763</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168660</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-06</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167027</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F141">
-        <v>515</v>
+        <v>2861</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168660</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-06</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167027</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>295</v>
+        <v>747</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168660</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-06</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148652</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F143">
-        <v>6914</v>
+        <v>1160</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172081</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-21</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148652</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F144">
-        <v>2479</v>
+        <v>1571</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172081</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-21</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148652</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F145">
-        <v>888</v>
+        <v>1568</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172081</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-21</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148652</t>
+          <t xml:space="preserve">2166742</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>590</v>
+        <v>427</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171998</t>
+          <t xml:space="preserve">311187261</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-21</t>
+          <t xml:space="preserve">2026-07-01</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">8856711</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F147">
-        <v>1420</v>
+        <v>1452</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177248</t>
+          <t xml:space="preserve">311193525</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">8856711</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F148">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177246</t>
+          <t xml:space="preserve">311193525</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2161012</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F149">
-        <v>748</v>
+        <v>350</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177248</t>
+          <t xml:space="preserve">311193760</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2161012</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F150">
-        <v>1834</v>
+        <v>350</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311193760</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2147649</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>3570</v>
+        <v>14739</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311196037</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2147256</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152">
-        <v>4129</v>
+        <v>2037</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311198248</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,35 +7631,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2165282</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F153">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311206384</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7681,35 +7681,35 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128107</t>
+          <t xml:space="preserve">8011213</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F154">
-        <v>8203</v>
+        <v>418</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178914</t>
+          <t xml:space="preserve">311209342</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7731,35 +7731,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F155">
-        <v>5505</v>
+        <v>291</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181218</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-06</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7781,35 +7781,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F156">
-        <v>8516</v>
+        <v>1543</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181218</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-06</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7831,35 +7831,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F157">
-        <v>763</v>
+        <v>408</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7881,35 +7881,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F158">
-        <v>2861</v>
+        <v>375</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7931,35 +7931,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F159">
-        <v>747</v>
+        <v>1414</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7981,35 +7981,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F160">
-        <v>1160</v>
+        <v>1539</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8031,35 +8031,35 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F161">
-        <v>1571</v>
+        <v>1500</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8081,35 +8081,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F162">
-        <v>1568</v>
+        <v>747</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166742</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F163">
-        <v>427</v>
+        <v>1534</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311187261</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-01</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8181,35 +8181,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147649</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F164">
-        <v>14739</v>
+        <v>1504</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196037</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147256</t>
+          <t xml:space="preserve">100083772</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,26 +8240,26 @@
         </is>
       </c>
       <c r="F165">
-        <v>2037</v>
+        <v>2615</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198248</t>
+          <t xml:space="preserve">311223010</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165282</t>
+          <t xml:space="preserve">8302179</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>1641</v>
+        <v>1328</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206384</t>
+          <t xml:space="preserve">311293200</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011213</t>
+          <t xml:space="preserve">8302179</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F167">
-        <v>418</v>
+        <v>2906</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209342</t>
+          <t xml:space="preserve">311293202</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">100083772</t>
+          <t xml:space="preserve">8302179</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F168">
-        <v>2615</v>
+        <v>7528</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223010</t>
+          <t xml:space="preserve">311293199</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-17</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8436,15 +8436,15 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F169">
-        <v>1328</v>
+        <v>671</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293200</t>
+          <t xml:space="preserve">311293197</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8486,15 +8486,15 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F170">
-        <v>2906</v>
+        <v>728</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293202</t>
+          <t xml:space="preserve">311293196</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8302179</t>
+          <t xml:space="preserve">2161792</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>7528</v>
+        <v>12189</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293199</t>
+          <t xml:space="preserve">311555945</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8302179</t>
+          <t xml:space="preserve">100217907</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F172">
-        <v>671</v>
+        <v>9567</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293197</t>
+          <t xml:space="preserve">311627918</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8302179</t>
+          <t xml:space="preserve">100213713</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>728</v>
+        <v>8659</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293196</t>
+          <t xml:space="preserve">311643661</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2032-11-19</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161792</t>
+          <t xml:space="preserve">100458771</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>12189</v>
+        <v>1798</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555945</t>
+          <t xml:space="preserve">311771834</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">100217907</t>
+          <t xml:space="preserve">2128107</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>9567</v>
+        <v>8203</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627918</t>
+          <t xml:space="preserve">311771690</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">100213713</t>
+          <t xml:space="preserve">2128107</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F176">
-        <v>8659</v>
+        <v>2025</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643661</t>
+          <t xml:space="preserve">311771690</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-19</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">100248845, 100248847</t>
+          <t xml:space="preserve">2128107</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F177">
-        <v>1512</v>
+        <v>792</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664049</t>
+          <t xml:space="preserve">311771690</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-03</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">100458771</t>
+          <t xml:space="preserve">100060348</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>1798</v>
+        <v>5039</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771834</t>
+          <t xml:space="preserve">311834579</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-05</t>
+          <t xml:space="preserve">2035-05-27</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">

--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:L179"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 514A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100248845, 100248847</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1512</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frødalen 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10208516</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>604</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brandhøjgårdsvej 2A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1303668</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>357</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenbuen 34</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">1304608</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>720</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Morelhaven 122</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128199</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>4250</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valbyvej 47A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146774</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1219</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valbyvej 47B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146774</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>2580</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbane Alle 4A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148852</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>906</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlotteager 7A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161091</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>5732</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>368</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1215</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>737</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>734</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rundageren 7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161248</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1262</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165282</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>735</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165621</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>324</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165621</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>514</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>352</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>352</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1587</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingstedvej 34</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201021</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1428</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">7010716</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>2278</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Snubbekorsvej 24B</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1340</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Snubbekorsvej 24B</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1463</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">714721, 2162134</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1904</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pile Alle 10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">7495520</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>285</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydskellet 1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">8011213</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>267</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 12A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>432</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 371A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161923</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>312</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">200019744</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterby Alle 15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128322</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>724</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">200019918</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landsbygaden 4A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142154</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>2362</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">200019887</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landsbygaden 4C</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142154</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>822</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">200019887</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landsbygaden 4B</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142154</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>810</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">200019887</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterby Alle 17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128322</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>557</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">200020052</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 1D</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128136</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>584</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311120438</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856618</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>357</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311120462</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856618</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>357</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311120462</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 7</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856618</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>377</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311120447</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856618</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>443</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311120447</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejtoften 1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147632</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>324</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311127421</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejtoften 3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147632</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>325</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311127428</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Græshøjvej 4A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1818</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311129908</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Græshøjvej 4A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>5611</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311129908</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Græshøjvej 4A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>2415</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311129908</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rundageren 15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>1064</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311129908</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 448</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1726</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311130107</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-20</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Græshøjvej 4B</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>525</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311131087</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Græshøjvej 4C</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161845</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>525</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311131087</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingstedvej 40</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201019</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>2111</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311131092</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkestien 2B</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142493</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>667</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311131989</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-31</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142054</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>357</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311132386</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rugvænget 24</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146021</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>324</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311133694</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rugvænget 26</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146021</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>374</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311133694</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 27</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2169189</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>526</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311133717</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 15</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">9208734</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>311</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311133714</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndvej 5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161612</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>359</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311134097</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-11</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndvej 4A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">8078292</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>375</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311134621</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 12A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167951</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>568</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311136636</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-25</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trekanten H 1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148252</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>485</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311138942</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Firkanten I 1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148252</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>438</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311138942</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fyrrekrattet 1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">7141252</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>780</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311138938</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenalderen 30</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2169509</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>405</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311141984</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingstedvej 33</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201300</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>469</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311142030</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stationsvej 6B</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161799</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>353</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311143240</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-03</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hallandsparken 1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127869</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>357</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311143917</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blåkildevej 22</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148250</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>359</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311143942</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blåkildevej 24</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148250</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>452</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311143941</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 3B</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161126</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>473</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311143930</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 3A</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161126</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>370</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311143927</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sankt Bendts Alle 8</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165627</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>365</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311143945</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marievej 2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146881</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>474</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311144172</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahornvej 1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146986</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>357</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311144177</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sankt Bendts Alle 2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165636</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>485</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311144235</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenmøllen 54</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201724</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>480</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311144396</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sønderby Torv 29</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">7141233</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>640</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311144459</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlotteager 226</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161123</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>547</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311144697</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevangshusene 65</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165634</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>357</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311144674</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brandvænget 9</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201285</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>547</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311144642</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyvelhaven 2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128200</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>623</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311145386</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fredensvej 1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147087</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>315</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311145474</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 371B</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161885</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>407</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311145515</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 371B</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161885</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>421</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311145515</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Magdavænget 2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2166063</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>310</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311145425</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 24</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>414</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311145440</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingstedvej 42</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2201022</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>295</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311145528</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrup Hovedgade 71</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146620</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>1796</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311145662</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppel Alle 12</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148830</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>3043</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311145619</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppel Alle 10</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148830</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>348</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311145623</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161127</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>495</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311145609</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>698</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>521</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>670</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>300</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>1467</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>678</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>3285</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 10</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856659</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>1250</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311145686</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1A</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">7613750</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>351</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311148755</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sankt Bendts Alle 6</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165627</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>390</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311149250</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 5</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165620</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>410</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311150128</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-14</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 9</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142499</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>1441</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311151831</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spangåvej 9</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2142499</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>408</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311151831</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 6</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">100015198</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>1632</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311152759</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 437C</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">8281272</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>456</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311152766</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 1A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">9622438</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>794</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311154284</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 1B</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">9622438</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>817</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311154284</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 1C</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">9622438</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>809</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311154281</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 1D</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">9622438</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>818</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311154284</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frøgård Alle 1E</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">9622438</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>794</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311154284</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrupgårdsvej 12</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2146071</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>1254</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311154518</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-19</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cirklen F 1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148249</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>381</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311155372</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cirklen G 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148249</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>381</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311155372</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østerby Alle 5</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127952</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>549</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311155980</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Espens Vænge 44</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147293</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>2473</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311155979</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lervangen 35</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127703</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>679</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311160370</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lervangen 35H</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127703</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>520</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311160369</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lervangen 35</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127703</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>1260</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311160371</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lervangen 35</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2127703</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>804</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311160367</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stationsvej 30</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161719</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>301</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311160365</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mølleholmen 3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147892</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>441</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311163055</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6081,33 +7291,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mølleholmen 7</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147892</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>361</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311163055</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6131,33 +7351,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højager 5</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t xml:space="preserve">9736444</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="H123">
         <v>319</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">311166156</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6181,33 +7411,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 54</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167027</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="H124">
         <v>303</v>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">311168660</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6231,33 +7471,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 54</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167027</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>515</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">311168660</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6281,33 +7531,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 54</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167027</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>295</v>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">311168660</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6331,33 +7591,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 76</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148652</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>6914</v>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t xml:space="preserve">311172081</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6381,33 +7651,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solsortevej 9B</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148652</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>2479</v>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t xml:space="preserve">311172081</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6431,33 +7711,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 76</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148652</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>888</v>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">311172081</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6481,33 +7771,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 74</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148652</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="H130">
         <v>590</v>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t xml:space="preserve">311171998</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6531,33 +7831,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 4</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="H131">
         <v>1420</v>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t xml:space="preserve">311177248</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6581,33 +7891,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrup Hovedgade 155</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="H132">
         <v>525</v>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">311177246</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6631,33 +7951,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 4</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="H133">
         <v>748</v>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">311177248</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6681,33 +8011,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Magdavænget 4</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="H134">
         <v>1834</v>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">311177242</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6731,33 +8071,43 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Magdavænget 4</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F135">
+      <c r="H135">
         <v>3570</v>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t xml:space="preserve">311177242</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="K135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6781,33 +8131,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Magdavænget 4</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F136">
+      <c r="H136">
         <v>4129</v>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t xml:space="preserve">311177242</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6831,33 +8191,43 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Magdavænget 4</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165865</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F137">
+      <c r="H137">
         <v>1645</v>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t xml:space="preserve">311177242</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6881,33 +8251,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fløng Byvej 24</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F138">
+      <c r="H138">
         <v>5505</v>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">311181218</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6931,33 +8311,43 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Soderupvej 13A</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2167945</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F139">
+      <c r="H139">
         <v>8516</v>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">311181218</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6981,33 +8371,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F140">
+      <c r="H140">
         <v>763</v>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7031,33 +8431,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F141">
+      <c r="H141">
         <v>2861</v>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7081,33 +8491,43 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F142">
+      <c r="H142">
         <v>747</v>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7131,33 +8551,43 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F143">
+      <c r="H143">
         <v>1160</v>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7181,33 +8611,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="H144">
         <v>1571</v>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7231,33 +8671,43 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161112</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F145">
+      <c r="H145">
         <v>1568</v>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t xml:space="preserve">311185316</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="J145" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7281,33 +8731,43 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valby Søndergade 2</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2166742</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F146">
+      <c r="H146">
         <v>427</v>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t xml:space="preserve">311187261</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-07-01</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7331,33 +8791,43 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kjeld Abells Plads 1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856711</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F147">
+      <c r="H147">
         <v>1452</v>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t xml:space="preserve">311193525</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="J147" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7381,33 +8851,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selsmosestræde 4</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t xml:space="preserve">8856711</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F148">
+      <c r="H148">
         <v>375</v>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t xml:space="preserve">311193525</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7431,33 +8911,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bomager 16</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161012</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F149">
+      <c r="H149">
         <v>350</v>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t xml:space="preserve">311193760</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7481,33 +8971,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topager 11</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161012</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F150">
+      <c r="H150">
         <v>350</v>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t xml:space="preserve">311193760</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7531,33 +9031,43 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mølleholmen 20</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147649</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F151">
+      <c r="H151">
         <v>14739</v>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t xml:space="preserve">311196037</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
+      <c r="K151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7581,33 +9091,43 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrup Hovedgade 86</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2147256</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F152">
+      <c r="H152">
         <v>2037</v>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t xml:space="preserve">311198248</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
+      <c r="K152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7631,33 +9151,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 4</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2165282</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F153">
+      <c r="H153">
         <v>1641</v>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t xml:space="preserve">311206384</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7681,33 +9211,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydskellet 1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
           <t xml:space="preserve">8011213</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F154">
+      <c r="H154">
         <v>418</v>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t xml:space="preserve">311209342</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="K154" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7731,33 +9271,43 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78A</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148414</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F155">
+      <c r="H155">
         <v>291</v>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="J155" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="K155" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7781,33 +9331,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78A</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148414</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F156">
+      <c r="H156">
         <v>1543</v>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7831,33 +9391,43 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78A</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148414</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F157">
+      <c r="H157">
         <v>408</v>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="J157" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="K157" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7881,33 +9451,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78B</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2148414</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F158">
+      <c r="H158">
         <v>375</v>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="J158" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="K158" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7931,33 +9511,43 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F159">
+      <c r="H159">
         <v>1414</v>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7981,33 +9571,43 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
       </c>
-      <c r="F160">
+      <c r="H160">
         <v>1539</v>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="J160" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="K160" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8031,33 +9631,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="F161">
+      <c r="H161">
         <v>1500</v>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="J161" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="K161" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8081,33 +9691,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c r="F162">
+      <c r="H162">
         <v>747</v>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="K162" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8131,33 +9751,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="F163">
+      <c r="H163">
         <v>1534</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8181,33 +9811,43 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 78</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
           <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
         </is>
       </c>
-      <c r="F164">
+      <c r="H164">
         <v>1504</v>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t xml:space="preserve">311218165</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8231,33 +9871,43 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sejlbjerg Alle 5</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
           <t xml:space="preserve">100083772</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F165">
+      <c r="H165">
         <v>2615</v>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t xml:space="preserve">311223010</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="J165" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8281,33 +9931,43 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torstorpvej 1</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
           <t xml:space="preserve">8302179</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F166">
+      <c r="H166">
         <v>1328</v>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t xml:space="preserve">311293200</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8331,33 +9991,43 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torstorpvej 1</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t xml:space="preserve">8302179</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F167">
+      <c r="H167">
         <v>2906</v>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t xml:space="preserve">311293202</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="J167" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8381,33 +10051,43 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torstorpvej 1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
           <t xml:space="preserve">8302179</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F168">
+      <c r="H168">
         <v>7528</v>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t xml:space="preserve">311293199</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="J168" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="K168" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8431,33 +10111,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torstorpvej 1</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
           <t xml:space="preserve">8302179</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F169">
+      <c r="H169">
         <v>671</v>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t xml:space="preserve">311293197</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="J169" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8481,33 +10171,43 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torstorpvej 1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
           <t xml:space="preserve">8302179</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F170">
+      <c r="H170">
         <v>728</v>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t xml:space="preserve">311293196</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="J170" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8531,33 +10231,43 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolebakken 1</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2161792</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F171">
+      <c r="H171">
         <v>12189</v>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t xml:space="preserve">311555945</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="J171" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8581,33 +10291,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrupgårdsvej 75</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
           <t xml:space="preserve">100217907</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F172">
+      <c r="H172">
         <v>9567</v>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t xml:space="preserve">311627918</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="J172" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8631,33 +10351,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusstræde 1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
           <t xml:space="preserve">100213713</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F173">
+      <c r="H173">
         <v>8659</v>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t xml:space="preserve">311643661</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-19</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8681,33 +10411,43 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taastrupgårdsvej 28A</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t xml:space="preserve">100458771</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F174">
+      <c r="H174">
         <v>1798</v>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t xml:space="preserve">311771834</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="J174" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8731,33 +10471,43 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128107</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F175">
+      <c r="H175">
         <v>8203</v>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="I175" t="inlineStr">
         <is>
           <t xml:space="preserve">311771690</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="J175" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8781,33 +10531,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128107</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F176">
+      <c r="H176">
         <v>2025</v>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t xml:space="preserve">311771690</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="J176" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8831,33 +10591,43 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gadehavegårdsvej 1B</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2128107</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F177">
+      <c r="H177">
         <v>792</v>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t xml:space="preserve">311771690</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="J177" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8881,33 +10651,43 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindehaven 2</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2630</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
           <t xml:space="preserve">100060348</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F178">
+      <c r="H178">
         <v>5039</v>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t xml:space="preserve">311834579</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="J178" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-27</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8931,39 +10711,49 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havtornvej 3</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2640</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
           <t xml:space="preserve">100209291</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F179">
+      <c r="H179">
         <v>1718</v>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t xml:space="preserve">311871402</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="J179" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J179"/>
+  <autoFilter ref="A1:L179"/>
 </worksheet>
 </file>
--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 514A</t>
+          <t xml:space="preserve">Brandhøjgårdsvej 2A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100248845, 100248847</t>
+          <t xml:space="preserve">1303668</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H2">
-        <v>1512</v>
+        <v>357</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødalen 1</t>
+          <t xml:space="preserve">Charlotteager 7A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10208516</t>
+          <t xml:space="preserve">2161091</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>604</v>
+        <v>5732</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandhøjgårdsvej 2A</t>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303668</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbuen 34</t>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304608</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H5">
-        <v>720</v>
+        <v>1215</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morelhaven 122</t>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128199</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H6">
-        <v>4250</v>
+        <v>737</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valbyvej 47A</t>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146774</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H7">
-        <v>1219</v>
+        <v>734</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valbyvej 47B</t>
+          <t xml:space="preserve">Charlottegårdsvej 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146774</t>
+          <t xml:space="preserve">714721, 2162134</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>2580</v>
+        <v>1904</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbane Alle 4A</t>
+          <t xml:space="preserve">Charlottegårdsvej 4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148852</t>
+          <t xml:space="preserve">7010716</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>906</v>
+        <v>2278</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlotteager 7A</t>
+          <t xml:space="preserve">Fløng Byvej 24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161091</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H10">
-        <v>5732</v>
+        <v>352</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1</t>
+          <t xml:space="preserve">Fløng Byvej 24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H11">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1</t>
+          <t xml:space="preserve">Fløng Byvej 26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H12">
-        <v>1215</v>
+        <v>1587</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1</t>
+          <t xml:space="preserve">Frødalen 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">10208516</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>737</v>
+        <v>604</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1</t>
+          <t xml:space="preserve">Jernbane Alle 4A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2148852</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>734</v>
+        <v>906</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rundageren 7</t>
+          <t xml:space="preserve">Lindehaven 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161248</t>
+          <t xml:space="preserve">2165621</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H15">
-        <v>1262</v>
+        <v>514</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindehaven 4</t>
+          <t xml:space="preserve">Lindehaven 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165282</t>
+          <t xml:space="preserve">2165621</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>735</v>
+        <v>324</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindehaven 3</t>
+          <t xml:space="preserve">Lindehaven 4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,16 +1001,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165621</t>
+          <t xml:space="preserve">2165282</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H17">
-        <v>324</v>
+        <v>735</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindehaven 1</t>
+          <t xml:space="preserve">Morelhaven 122</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165621</t>
+          <t xml:space="preserve">2128199</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>514</v>
+        <v>4250</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 24</t>
+          <t xml:space="preserve">Pile Alle 10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">7495520</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 24</t>
+          <t xml:space="preserve">Rundageren 7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">2161248</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>352</v>
+        <v>1262</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 26</t>
+          <t xml:space="preserve">Snubbekorsvej 24B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>1587</v>
+        <v>1340</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstedvej 34</t>
+          <t xml:space="preserve">Snubbekorsvej 24B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201021</t>
+          <t xml:space="preserve">714196, 8856710</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>1428</v>
+        <v>1463</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 4</t>
+          <t xml:space="preserve">Spangåvej 12A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010716</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H23">
-        <v>2278</v>
+        <v>432</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snubbekorsvej 24B</t>
+          <t xml:space="preserve">Stenbuen 34</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">714196, 8856710</t>
+          <t xml:space="preserve">1304608</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="H24">
-        <v>1340</v>
+        <v>720</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snubbekorsvej 24B</t>
+          <t xml:space="preserve">Sydskellet 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">714196, 8856710</t>
+          <t xml:space="preserve">8011213</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H25">
-        <v>1463</v>
+        <v>267</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 2</t>
+          <t xml:space="preserve">Tingstedvej 34</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">714721, 2162134</t>
+          <t xml:space="preserve">2201021</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H26">
-        <v>1904</v>
+        <v>1428</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 10</t>
+          <t xml:space="preserve">Valbyvej 47A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7495520</t>
+          <t xml:space="preserve">2146774</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>285</v>
+        <v>1219</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydskellet 1</t>
+          <t xml:space="preserve">Valbyvej 47B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011213</t>
+          <t xml:space="preserve">2146774</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>267</v>
+        <v>2580</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,40 +1711,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangåvej 12A</t>
+          <t xml:space="preserve">Hovedgaden 371A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">2161923</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>432</v>
+        <v>312</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019744</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 371A</t>
+          <t xml:space="preserve">Landsbygaden 4A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161923</t>
+          <t xml:space="preserve">2142154</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>312</v>
+        <v>2362</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019744</t>
+          <t xml:space="preserve">200019887</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-31</t>
+          <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterby Alle 15</t>
+          <t xml:space="preserve">Landsbygaden 4B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,20 +1841,20 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128322</t>
+          <t xml:space="preserve">2142154</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H31">
-        <v>724</v>
+        <v>810</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019918</t>
+          <t xml:space="preserve">200019887</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landsbygaden 4A</t>
+          <t xml:space="preserve">Landsbygaden 4C</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1906,11 +1906,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H32">
-        <v>2362</v>
+        <v>822</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landsbygaden 4C</t>
+          <t xml:space="preserve">Vesterby Alle 15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142154</t>
+          <t xml:space="preserve">2128322</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>822</v>
+        <v>724</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019887</t>
+          <t xml:space="preserve">200019918</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landsbygaden 4B</t>
+          <t xml:space="preserve">Vesterby Alle 17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142154</t>
+          <t xml:space="preserve">2128322</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="H34">
-        <v>810</v>
+        <v>557</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019887</t>
+          <t xml:space="preserve">200020052</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-03</t>
+          <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterby Alle 17</t>
+          <t xml:space="preserve">Gadehavegårdsvej 1D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128322</t>
+          <t xml:space="preserve">2128136</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020052</t>
+          <t xml:space="preserve">311120438</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-07</t>
+          <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 1D</t>
+          <t xml:space="preserve">Gadehavegårdsvej 3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128136</t>
+          <t xml:space="preserve">8856618</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,11 +2150,11 @@
         </is>
       </c>
       <c r="H36">
-        <v>584</v>
+        <v>357</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120438</t>
+          <t xml:space="preserve">311120462</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 3</t>
+          <t xml:space="preserve">Gadehavegårdsvej 5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H37">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 5</t>
+          <t xml:space="preserve">Gadehavegårdsvej 7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2266,15 +2266,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120462</t>
+          <t xml:space="preserve">311120447</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 7</t>
+          <t xml:space="preserve">Gadehavegårdsvej 9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2326,11 +2326,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H39">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 9</t>
+          <t xml:space="preserve">Vejtoften 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856618</t>
+          <t xml:space="preserve">2147632</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120447</t>
+          <t xml:space="preserve">311127421</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-22</t>
+          <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejtoften 1</t>
+          <t xml:space="preserve">Vejtoften 3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,15 +2446,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127421</t>
+          <t xml:space="preserve">311127428</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejtoften 3</t>
+          <t xml:space="preserve">Græshøjvej 4A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147632</t>
+          <t xml:space="preserve">2161845</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>325</v>
+        <v>1818</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127428</t>
+          <t xml:space="preserve">311129908</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-03</t>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2566,11 +2566,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H43">
-        <v>1818</v>
+        <v>5611</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H44">
-        <v>5611</v>
+        <v>2415</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshøjvej 4A</t>
+          <t xml:space="preserve">Rundageren 15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2686,11 +2686,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H45">
-        <v>2415</v>
+        <v>1064</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rundageren 15</t>
+          <t xml:space="preserve">Hovedgaden 448</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>1064</v>
+        <v>1726</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311129908</t>
+          <t xml:space="preserve">311130107</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-19</t>
+          <t xml:space="preserve">2025-08-20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 448</t>
+          <t xml:space="preserve">Græshøjvej 4B</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2806,20 +2806,20 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H47">
-        <v>1726</v>
+        <v>525</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311130107</t>
+          <t xml:space="preserve">311131087</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-20</t>
+          <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshøjvej 4B</t>
+          <t xml:space="preserve">Græshøjvej 4C</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H48">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshøjvej 4C</t>
+          <t xml:space="preserve">Tingstedvej 40</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,20 +2921,20 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161845</t>
+          <t xml:space="preserve">2201019</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
-        <v>525</v>
+        <v>2111</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131087</t>
+          <t xml:space="preserve">311131092</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstedvej 40</t>
+          <t xml:space="preserve">Kirkestien 2B</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201019</t>
+          <t xml:space="preserve">2142493</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>2111</v>
+        <v>667</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131092</t>
+          <t xml:space="preserve">311131989</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-26</t>
+          <t xml:space="preserve">2025-08-31</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestien 2B</t>
+          <t xml:space="preserve">Spangåvej 12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142493</t>
+          <t xml:space="preserve">2142054</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>667</v>
+        <v>357</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311131989</t>
+          <t xml:space="preserve">311132386</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-31</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangåvej 12</t>
+          <t xml:space="preserve">Fløng Byvej 15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142054</t>
+          <t xml:space="preserve">9208734</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132386</t>
+          <t xml:space="preserve">311133714</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugvænget 24</t>
+          <t xml:space="preserve">Fløng Byvej 27</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146021</t>
+          <t xml:space="preserve">2169189</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,11 +3170,11 @@
         </is>
       </c>
       <c r="H53">
-        <v>324</v>
+        <v>526</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133694</t>
+          <t xml:space="preserve">311133717</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugvænget 26</t>
+          <t xml:space="preserve">Rugvænget 24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3226,11 +3226,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,30 +3271,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 27</t>
+          <t xml:space="preserve">Rugvænget 26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169189</t>
+          <t xml:space="preserve">2146021</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133717</t>
+          <t xml:space="preserve">311133694</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 15</t>
+          <t xml:space="preserve">Brøndvej 5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208734</t>
+          <t xml:space="preserve">2161612</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133714</t>
+          <t xml:space="preserve">311134097</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-09-11</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndvej 5</t>
+          <t xml:space="preserve">Brøndvej 4A</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161612</t>
+          <t xml:space="preserve">8078292</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134097</t>
+          <t xml:space="preserve">311134621</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-11</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndvej 4A</t>
+          <t xml:space="preserve">Fløng Byvej 12A</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8078292</t>
+          <t xml:space="preserve">2167951</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>375</v>
+        <v>568</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134621</t>
+          <t xml:space="preserve">311136636</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-15</t>
+          <t xml:space="preserve">2025-09-25</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 12A</t>
+          <t xml:space="preserve">Firkanten I 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167951</t>
+          <t xml:space="preserve">2148252</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>568</v>
+        <v>438</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136636</t>
+          <t xml:space="preserve">311138942</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-25</t>
+          <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekanten H 1</t>
+          <t xml:space="preserve">Fyrrekrattet 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148252</t>
+          <t xml:space="preserve">7141252</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,11 +3590,11 @@
         </is>
       </c>
       <c r="H60">
-        <v>485</v>
+        <v>780</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138942</t>
+          <t xml:space="preserve">311138938</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firkanten I 1</t>
+          <t xml:space="preserve">Trekanten H 1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3646,11 +3646,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrrekrattet 1</t>
+          <t xml:space="preserve">Stenalderen 30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7141252</t>
+          <t xml:space="preserve">2169509</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="H62">
-        <v>780</v>
+        <v>405</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138938</t>
+          <t xml:space="preserve">311141984</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-08</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenalderen 30</t>
+          <t xml:space="preserve">Tingstedvej 33</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169509</t>
+          <t xml:space="preserve">2201300</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,11 +3770,11 @@
         </is>
       </c>
       <c r="H63">
-        <v>405</v>
+        <v>469</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141984</t>
+          <t xml:space="preserve">311142030</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstedvej 33</t>
+          <t xml:space="preserve">Stationsvej 6B</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201300</t>
+          <t xml:space="preserve">2161799</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,16 +3830,16 @@
         </is>
       </c>
       <c r="H64">
-        <v>469</v>
+        <v>353</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142030</t>
+          <t xml:space="preserve">311143240</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-03</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 6B</t>
+          <t xml:space="preserve">Blåkildevej 22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161799</t>
+          <t xml:space="preserve">2148250</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143240</t>
+          <t xml:space="preserve">311143942</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-03</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hallandsparken 1</t>
+          <t xml:space="preserve">Blåkildevej 24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,20 +3941,20 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127869</t>
+          <t xml:space="preserve">2148250</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>357</v>
+        <v>452</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143917</t>
+          <t xml:space="preserve">311143941</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,30 +3991,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blåkildevej 22</t>
+          <t xml:space="preserve">Charlottegårdsvej 3A</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148250</t>
+          <t xml:space="preserve">2161126</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H67">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143942</t>
+          <t xml:space="preserve">311143927</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,30 +4051,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blåkildevej 24</t>
+          <t xml:space="preserve">Charlottegårdsvej 3B</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148250</t>
+          <t xml:space="preserve">2161126</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H68">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143941</t>
+          <t xml:space="preserve">311143930</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 3B</t>
+          <t xml:space="preserve">Hallandsparken 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161126</t>
+          <t xml:space="preserve">2127869</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="H69">
-        <v>473</v>
+        <v>357</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143930</t>
+          <t xml:space="preserve">311143917</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 3A</t>
+          <t xml:space="preserve">Sankt Bendts Alle 8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161126</t>
+          <t xml:space="preserve">2165627</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,11 +4190,11 @@
         </is>
       </c>
       <c r="H70">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143927</t>
+          <t xml:space="preserve">311143945</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Bendts Alle 8</t>
+          <t xml:space="preserve">Ahornvej 1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,25 +4241,25 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165627</t>
+          <t xml:space="preserve">2146986</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143945</t>
+          <t xml:space="preserve">311144177</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 1</t>
+          <t xml:space="preserve">Sankt Bendts Alle 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146986</t>
+          <t xml:space="preserve">2165636</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="H73">
-        <v>357</v>
+        <v>485</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144177</t>
+          <t xml:space="preserve">311144235</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Bendts Alle 2</t>
+          <t xml:space="preserve">Stenmøllen 54</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165636</t>
+          <t xml:space="preserve">2201724</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144235</t>
+          <t xml:space="preserve">311144396</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenmøllen 54</t>
+          <t xml:space="preserve">Sønderby Torv 29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201724</t>
+          <t xml:space="preserve">7141233</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>480</v>
+        <v>640</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144396</t>
+          <t xml:space="preserve">311144459</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderby Torv 29</t>
+          <t xml:space="preserve">Brandvænget 9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7141233</t>
+          <t xml:space="preserve">2201285</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>640</v>
+        <v>547</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144459</t>
+          <t xml:space="preserve">311144642</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandvænget 9</t>
+          <t xml:space="preserve">Fløng Byvej 24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201285</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H79">
-        <v>547</v>
+        <v>414</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144642</t>
+          <t xml:space="preserve">311145440</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-11</t>
+          <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelhaven 2</t>
+          <t xml:space="preserve">Fredensvej 1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128200</t>
+          <t xml:space="preserve">2147087</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,11 +4790,11 @@
         </is>
       </c>
       <c r="H80">
-        <v>623</v>
+        <v>315</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145386</t>
+          <t xml:space="preserve">311145474</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1</t>
+          <t xml:space="preserve">Gyvelhaven 2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147087</t>
+          <t xml:space="preserve">2128200</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>315</v>
+        <v>623</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145474</t>
+          <t xml:space="preserve">311145386</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 24</t>
+          <t xml:space="preserve">Tingstedvej 42</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">2201022</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>414</v>
+        <v>295</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145440</t>
+          <t xml:space="preserve">311145528</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstedvej 42</t>
+          <t xml:space="preserve">Charlottegårdsvej 5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201022</t>
+          <t xml:space="preserve">2161127</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145528</t>
+          <t xml:space="preserve">311145609</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-16</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrup Hovedgade 71</t>
+          <t xml:space="preserve">Poppel Alle 10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,20 +5201,20 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146620</t>
+          <t xml:space="preserve">2148830</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H87">
-        <v>1796</v>
+        <v>348</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145662</t>
+          <t xml:space="preserve">311145623</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 10</t>
+          <t xml:space="preserve">Spangåvej 10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,20 +5321,20 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148830</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>348</v>
+        <v>698</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145623</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,30 +5371,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 5</t>
+          <t xml:space="preserve">Spangåvej 10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161127</t>
+          <t xml:space="preserve">8856659</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H90">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145609</t>
+          <t xml:space="preserve">311145686</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5446,11 +5446,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H91">
-        <v>698</v>
+        <v>670</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5506,11 +5506,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H92">
-        <v>521</v>
+        <v>300</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5566,11 +5566,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H93">
-        <v>670</v>
+        <v>1467</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5626,11 +5626,11 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H94">
-        <v>300</v>
+        <v>678</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H95">
-        <v>1467</v>
+        <v>3285</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5746,11 +5746,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H96">
-        <v>678</v>
+        <v>1250</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangåvej 10</t>
+          <t xml:space="preserve">Taastrup Hovedgade 71</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,20 +5801,20 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">2146620</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>3285</v>
+        <v>1796</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311145662</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangåvej 10</t>
+          <t xml:space="preserve">Charlottegårdsvej 1A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856659</t>
+          <t xml:space="preserve">7613750</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>1250</v>
+        <v>351</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145686</t>
+          <t xml:space="preserve">311148755</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1A</t>
+          <t xml:space="preserve">Sankt Bendts Alle 6</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7613750</t>
+          <t xml:space="preserve">2165627</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148755</t>
+          <t xml:space="preserve">311149250</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Bendts Alle 6</t>
+          <t xml:space="preserve">Lindehaven 5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165627</t>
+          <t xml:space="preserve">2165620</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149250</t>
+          <t xml:space="preserve">311150128</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2025-12-14</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindehaven 5</t>
+          <t xml:space="preserve">Spangåvej 9</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165620</t>
+          <t xml:space="preserve">2142499</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>410</v>
+        <v>1441</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150128</t>
+          <t xml:space="preserve">311151831</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-14</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H102">
-        <v>1441</v>
+        <v>408</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangåvej 9</t>
+          <t xml:space="preserve">Frøgård Alle 6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142499</t>
+          <t xml:space="preserve">100015198</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H103">
-        <v>408</v>
+        <v>1632</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311151831</t>
+          <t xml:space="preserve">311152759</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,30 +6211,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 6</t>
+          <t xml:space="preserve">Hovedgaden 437C</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100015198</t>
+          <t xml:space="preserve">8281272</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>1632</v>
+        <v>456</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152759</t>
+          <t xml:space="preserve">311152766</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 437C</t>
+          <t xml:space="preserve">Frøgård Alle 1A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8281272</t>
+          <t xml:space="preserve">9622438</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>456</v>
+        <v>794</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152766</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-07</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 1A</t>
+          <t xml:space="preserve">Frøgård Alle 1B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H106">
-        <v>794</v>
+        <v>817</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 1B</t>
+          <t xml:space="preserve">Frøgård Alle 1C</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6406,15 +6406,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H107">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311154281</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 1C</t>
+          <t xml:space="preserve">Frøgård Alle 1D</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6466,15 +6466,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H108">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154281</t>
+          <t xml:space="preserve">311154284</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 1D</t>
+          <t xml:space="preserve">Frøgård Alle 1E</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6526,11 +6526,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H109">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøgård Alle 1E</t>
+          <t xml:space="preserve">Taastrupgårdsvej 12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622438</t>
+          <t xml:space="preserve">2146071</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>794</v>
+        <v>1254</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154284</t>
+          <t xml:space="preserve">311154518</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-18</t>
+          <t xml:space="preserve">2026-01-19</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrupgårdsvej 12</t>
+          <t xml:space="preserve">Cirklen F 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146071</t>
+          <t xml:space="preserve">2148249</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>1254</v>
+        <v>381</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311154518</t>
+          <t xml:space="preserve">311155372</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-19</t>
+          <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cirklen F 1</t>
+          <t xml:space="preserve">Cirklen G 1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H112">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cirklen G 1</t>
+          <t xml:space="preserve">Espens Vænge 44</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,25 +6761,25 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148249</t>
+          <t xml:space="preserve">2147293</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>381</v>
+        <v>2473</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155372</t>
+          <t xml:space="preserve">311155979</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-25</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espens Vænge 44</t>
+          <t xml:space="preserve">Lervangen 35</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147293</t>
+          <t xml:space="preserve">2127703</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="H115">
-        <v>2473</v>
+        <v>679</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155979</t>
+          <t xml:space="preserve">311160370</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6946,15 +6946,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>679</v>
+        <v>1260</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160370</t>
+          <t xml:space="preserve">311160371</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lervangen 35H</t>
+          <t xml:space="preserve">Lervangen 35</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7006,15 +7006,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H117">
-        <v>520</v>
+        <v>804</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160369</t>
+          <t xml:space="preserve">311160367</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lervangen 35</t>
+          <t xml:space="preserve">Lervangen 35H</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7066,15 +7066,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H118">
-        <v>1260</v>
+        <v>520</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160371</t>
+          <t xml:space="preserve">311160369</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lervangen 35</t>
+          <t xml:space="preserve">Stationsvej 30</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127703</t>
+          <t xml:space="preserve">2161719</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H119">
-        <v>804</v>
+        <v>301</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160367</t>
+          <t xml:space="preserve">311160365</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 30</t>
+          <t xml:space="preserve">Mølleholmen 3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161719</t>
+          <t xml:space="preserve">2147892</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="H120">
-        <v>301</v>
+        <v>441</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311160365</t>
+          <t xml:space="preserve">311163055</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-23</t>
+          <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mølleholmen 3</t>
+          <t xml:space="preserve">Mølleholmen 7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7246,11 +7246,11 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H121">
-        <v>441</v>
+        <v>361</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mølleholmen 7</t>
+          <t xml:space="preserve">Højager 5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,25 +7301,25 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147892</t>
+          <t xml:space="preserve">9736444</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163055</t>
+          <t xml:space="preserve">311166156</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-08</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højager 5</t>
+          <t xml:space="preserve">Skolevej 54</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9736444</t>
+          <t xml:space="preserve">2167027</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166156</t>
+          <t xml:space="preserve">311168660</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>303</v>
+        <v>515</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7486,11 +7486,11 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H125">
-        <v>515</v>
+        <v>295</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 54</t>
+          <t xml:space="preserve">Parkvej 74</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167027</t>
+          <t xml:space="preserve">2148652</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="H126">
-        <v>295</v>
+        <v>590</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168660</t>
+          <t xml:space="preserve">311171998</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-06</t>
+          <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsortevej 9B</t>
+          <t xml:space="preserve">Parkvej 76</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7666,11 +7666,11 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H128">
-        <v>2479</v>
+        <v>888</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 76</t>
+          <t xml:space="preserve">Solsortevej 9B</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H129">
-        <v>888</v>
+        <v>2479</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 74</t>
+          <t xml:space="preserve">Magdavænget 4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148652</t>
+          <t xml:space="preserve">2165865</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>590</v>
+        <v>1834</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171998</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-21</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Magdavænget 4</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7846,15 +7846,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H131">
-        <v>1420</v>
+        <v>3570</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177248</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrup Hovedgade 155</t>
+          <t xml:space="preserve">Magdavænget 4</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7906,15 +7906,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H132">
-        <v>525</v>
+        <v>4129</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177246</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Magdavænget 4</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7966,15 +7966,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H133">
-        <v>748</v>
+        <v>1645</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177248</t>
+          <t xml:space="preserve">311177242</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magdavænget 4</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8026,15 +8026,15 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H134">
-        <v>1834</v>
+        <v>1420</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311177248</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magdavænget 4</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8086,15 +8086,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H135">
-        <v>3570</v>
+        <v>748</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311177248</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magdavænget 4</t>
+          <t xml:space="preserve">Taastrup Hovedgade 155</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8146,15 +8146,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H136">
-        <v>4129</v>
+        <v>525</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311177246</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magdavænget 4</t>
+          <t xml:space="preserve">Fløng Byvej 24</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165865</t>
+          <t xml:space="preserve">2167945</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>1645</v>
+        <v>5505</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311177242</t>
+          <t xml:space="preserve">311181218</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fløng Byvej 24</t>
+          <t xml:space="preserve">Soderupvej 13A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8266,11 +8266,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>5505</v>
+        <v>8516</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soderupvej 13A</t>
+          <t xml:space="preserve">Charlottegårdsvej 1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,25 +8321,25 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167945</t>
+          <t xml:space="preserve">2161112</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>8516</v>
+        <v>763</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181218</t>
+          <t xml:space="preserve">311185316</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-06</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8386,11 +8386,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H140">
-        <v>763</v>
+        <v>2861</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8446,11 +8446,11 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H141">
-        <v>2861</v>
+        <v>747</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -8506,11 +8506,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H142">
-        <v>747</v>
+        <v>1160</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H143">
-        <v>1160</v>
+        <v>1571</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H144">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottegårdsvej 1</t>
+          <t xml:space="preserve">Valby Søndergade 2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161112</t>
+          <t xml:space="preserve">2166742</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
-        <v>1568</v>
+        <v>427</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185316</t>
+          <t xml:space="preserve">311187261</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2026-07-01</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valby Søndergade 2</t>
+          <t xml:space="preserve">Kjeld Abells Plads 1</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,25 +8741,25 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166742</t>
+          <t xml:space="preserve">8856711</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H146">
-        <v>427</v>
+        <v>1452</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311187261</t>
+          <t xml:space="preserve">311193525</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-01</t>
+          <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeld Abells Plads 1</t>
+          <t xml:space="preserve">Selsmosestræde 4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8806,11 +8806,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H147">
-        <v>1452</v>
+        <v>375</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selsmosestræde 4</t>
+          <t xml:space="preserve">Bomager 16</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8856711</t>
+          <t xml:space="preserve">2161012</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H148">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193525</t>
+          <t xml:space="preserve">311193760</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-09</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bomager 16</t>
+          <t xml:space="preserve">Topager 11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149">
@@ -8971,35 +8971,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topager 11</t>
+          <t xml:space="preserve">Mølleholmen 20</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161012</t>
+          <t xml:space="preserve">2147649</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H150">
-        <v>350</v>
+        <v>14739</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193760</t>
+          <t xml:space="preserve">311196037</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mølleholmen 20</t>
+          <t xml:space="preserve">Taastrup Hovedgade 86</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147649</t>
+          <t xml:space="preserve">2147256</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H151">
-        <v>14739</v>
+        <v>2037</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196037</t>
+          <t xml:space="preserve">311198248</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrup Hovedgade 86</t>
+          <t xml:space="preserve">Lindehaven 4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,35 +9101,35 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147256</t>
+          <t xml:space="preserve">2165282</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H152">
-        <v>2037</v>
+        <v>1641</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198248</t>
+          <t xml:space="preserve">311206384</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindehaven 4</t>
+          <t xml:space="preserve">Sydskellet 1</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,25 +9161,25 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2165282</t>
+          <t xml:space="preserve">8011213</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H153">
-        <v>1641</v>
+        <v>418</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206384</t>
+          <t xml:space="preserve">311209342</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydskellet 1</t>
+          <t xml:space="preserve">Parkvej 78</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011213</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H154">
-        <v>418</v>
+        <v>1414</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209342</t>
+          <t xml:space="preserve">311218165</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78A</t>
+          <t xml:space="preserve">Parkvej 78</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,16 +9281,16 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H155">
-        <v>291</v>
+        <v>1539</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78A</t>
+          <t xml:space="preserve">Parkvej 78</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,16 +9341,16 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H156">
-        <v>1543</v>
+        <v>1500</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78A</t>
+          <t xml:space="preserve">Parkvej 78</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,16 +9401,16 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H157">
-        <v>408</v>
+        <v>747</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78B</t>
+          <t xml:space="preserve">Parkvej 78</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9461,16 +9461,16 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148414</t>
+          <t xml:space="preserve">714120, 2148414</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H158">
-        <v>375</v>
+        <v>1534</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9526,11 +9526,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H159">
-        <v>1414</v>
+        <v>1504</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78</t>
+          <t xml:space="preserve">Parkvej 78A</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,16 +9581,16 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H160">
-        <v>1539</v>
+        <v>291</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78</t>
+          <t xml:space="preserve">Parkvej 78A</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,16 +9641,16 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H161">
-        <v>1500</v>
+        <v>1543</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78</t>
+          <t xml:space="preserve">Parkvej 78A</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,16 +9701,16 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H162">
-        <v>747</v>
+        <v>408</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78</t>
+          <t xml:space="preserve">Parkvej 78B</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,16 +9761,16 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">2148414</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H163">
-        <v>1534</v>
+        <v>375</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 78</t>
+          <t xml:space="preserve">Sejlbjerg Alle 5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">714120, 2148414</t>
+          <t xml:space="preserve">100083772</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>1504</v>
+        <v>2615</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218165</t>
+          <t xml:space="preserve">311223010</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlbjerg Alle 5</t>
+          <t xml:space="preserve">Torstorpvej 1</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100083772</t>
+          <t xml:space="preserve">8302179</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="H165">
-        <v>2615</v>
+        <v>1328</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223010</t>
+          <t xml:space="preserve">311293200</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-17</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9946,15 +9946,15 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H166">
-        <v>1328</v>
+        <v>2906</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293200</t>
+          <t xml:space="preserve">311293202</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10006,15 +10006,15 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H167">
-        <v>2906</v>
+        <v>7528</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293202</t>
+          <t xml:space="preserve">311293199</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10066,15 +10066,15 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H168">
-        <v>7528</v>
+        <v>671</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293199</t>
+          <t xml:space="preserve">311293197</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10126,15 +10126,15 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H169">
-        <v>671</v>
+        <v>728</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293197</t>
+          <t xml:space="preserve">311293196</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,35 +10171,35 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torstorpvej 1</t>
+          <t xml:space="preserve">Skolebakken 1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8302179</t>
+          <t xml:space="preserve">2161792</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>728</v>
+        <v>12189</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293196</t>
+          <t xml:space="preserve">311555945</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 1</t>
+          <t xml:space="preserve">Taastrupgårdsvej 75</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2640</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161792</t>
+          <t xml:space="preserve">100217907</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10250,16 +10250,16 @@
         </is>
       </c>
       <c r="H171">
-        <v>12189</v>
+        <v>9567</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555945</t>
+          <t xml:space="preserve">311627918</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrupgårdsvej 75</t>
+          <t xml:space="preserve">Rådhusstræde 1</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100217907</t>
+          <t xml:space="preserve">100213713</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10310,16 +10310,16 @@
         </is>
       </c>
       <c r="H172">
-        <v>9567</v>
+        <v>8659</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627918</t>
+          <t xml:space="preserve">311643661</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2032-11-19</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,17 +10351,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusstræde 1</t>
+          <t xml:space="preserve">Hovedgaden 514A</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2640</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">100213713</t>
+          <t xml:space="preserve">100248845, 100248847</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10370,16 +10370,16 @@
         </is>
       </c>
       <c r="H173">
-        <v>8659</v>
+        <v>1512</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643661</t>
+          <t xml:space="preserve">311664049</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-19</t>
+          <t xml:space="preserve">2033-03-03</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taastrupgårdsvej 28A</t>
+          <t xml:space="preserve">Gadehavegårdsvej 1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">100458771</t>
+          <t xml:space="preserve">2128107</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10430,11 +10430,11 @@
         </is>
       </c>
       <c r="H174">
-        <v>1798</v>
+        <v>8203</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771834</t>
+          <t xml:space="preserve">311771690</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H175">
-        <v>8203</v>
+        <v>2025</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 1</t>
+          <t xml:space="preserve">Gadehavegårdsvej 1B</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10546,11 +10546,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H176">
-        <v>2025</v>
+        <v>792</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadehavegårdsvej 1B</t>
+          <t xml:space="preserve">Taastrupgårdsvej 28A</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,20 +10601,20 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128107</t>
+          <t xml:space="preserve">100458771</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H177">
-        <v>792</v>
+        <v>1798</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771690</t>
+          <t xml:space="preserve">311771834</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">

--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:M179"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-31</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-03</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-22</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-03</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-20</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-26</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-31</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-11</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-25</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-08</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-03</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-11</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-16</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-14</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-19</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-25</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-23</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-08</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-06</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-21</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-01</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Udløbet</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitekt &amp; ByggeService</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-19</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-03</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-27</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,21 +11629,26 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L179"/>
+  <autoFilter ref="A1:M179"/>
 </worksheet>
 </file>